--- a/Tejas_Agrawal_Rirekisho.xlsx
+++ b/Tejas_Agrawal_Rirekisho.xlsx
@@ -122,19 +122,10 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日本語能力試験</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">(JLPT)N1 </t>
+      <t xml:space="preserve">AWS Cloud Practitioner </t>
     </r>
     <r>
       <rPr>
@@ -143,7 +134,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">受験予定 </t>
+      <t xml:space="preserve">取得 </t>
     </r>
   </si>
   <si>
@@ -507,7 +498,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">　　　約　　時間　　分</t>
+    <t xml:space="preserve">　　　約　　時間　30分</t>
   </si>
   <si>
     <t xml:space="preserve">専門学校東京クールジャパン・アカデミー ゲーム総合学科 ゲームプログラマー専攻 卒業</t>
@@ -672,14 +663,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1287,9 +1278,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>556560</xdr:colOff>
+      <xdr:colOff>556200</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>61560</xdr:rowOff>
+      <xdr:rowOff>61200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1299,7 +1290,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6285240" y="177840"/>
-          <a:ext cx="1379520" cy="1779120"/>
+          <a:ext cx="1379160" cy="1778760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1698,9 +1689,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>576360</xdr:colOff>
+      <xdr:colOff>576000</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>92880</xdr:rowOff>
+      <xdr:rowOff>92520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1714,7 +1705,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6268680" y="144720"/>
-          <a:ext cx="1415880" cy="1843560"/>
+          <a:ext cx="1415520" cy="1843200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2897,7 +2888,7 @@
         <v>2026</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q32" s="50" t="s">
         <v>32</v>
